--- a/processed_ruby_restored_xlsx/sc236_凛８：バスの中.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc236_凛８：バスの中.ss.xlsx
@@ -514,8 +514,8 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>On a fine sunny day, I was in a good mood cleaning the
-house.</t>
+          <t>On a fine sunny day, I was in a good mood cleaning
+the house.</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -577,8 +577,8 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>It looked like Miru-chan was paired with Rin-chan, and
-Rurichiyo-chan with Nono-chan.</t>
+          <t>It looked like Miru-chan was paired with Rin-chan,
+and Rurichiyo-chan with Nono-chan.</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1004,8 +1004,8 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>I nodded and went back to cleaning, and Nono-chan came
-over.</t>
+          <t>I nodded and went back to cleaning, and Nono-chan
+came over.</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1265,8 +1265,8 @@
       <c r="B53" s="1" t="inlineStr">
         <is>
           <t>...Maybe my way of putting it was bad; their
-imaginations seem to have blown way up between the two
-of them.</t>
+imaginations seem to have blown way up between the
+two of them.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1312,8 +1312,8 @@
       <c r="B56" s="1" t="inlineStr">
         <is>
           <t>Maybe the game's reached a stopping point, Miru-chan
-looked up from the screen and, laughing, turned toward
-us.</t>
+looked up from the screen and, laughing, turned
+toward us.</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1572,8 +1572,8 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>「Muu... but I'm surprised this little game console can
-do real-time chat！」</t>
+          <t>「Muu... but I'm surprised this little game console
+can do real-time chat！」</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2076,8 +2076,8 @@
       <c r="B106" s="1" t="inlineStr">
         <is>
           <t>I brought the game console from the room and set up a
-group chat with Miru-chan, Rin-chan, and four consoles
-total.</t>
+group chat with Miru-chan, Rin-chan, and four
+consoles total.</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2215,8 +2215,8 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>「Yes... I'm still a bit unsure, but if you think of it
-like email, it'll be fine.」</t>
+          <t>「Yes... I'm still a bit unsure, but if you think of
+it like email, it'll be fine.」</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3315,8 +3315,8 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>「More importantly, MiruMiru and Rurichiyo replied too,
-you know？」</t>
+          <t>「More importantly, MiruMiru and Rurichiyo replied
+too, you know？」</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3451,7 +3451,8 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>When I asked back in surprise, Rin-chan grinned again.</t>
+          <t>When I asked back in surprise, Rin-chan grinned
+again.</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3574,7 +3575,8 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>「...Well then, shall I see what you've got, Rin-chan？」</t>
+          <t>「...Well then, shall I see what you've got,
+Rin-chan？」</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3698,8 +3700,8 @@
       <c r="B212" s="1" t="inlineStr">
         <is>
           <t>I get that she's being considerate of Nono-chan, who
-made herself the demon... but are they really going to
-sacrifice Miru-chan...?</t>
+made herself the demon... but are they really going
+to sacrifice Miru-chan...?</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3927,8 +3929,8 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>However, if they're on the same floor, she wouldn't be
-able to move without risk.</t>
+          <t>However, if they're on the same floor, she wouldn't
+be able to move without risk.</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3977,9 +3979,9 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan was upstairs and Miru-chan, who was about to
-move from her hiding spot, ended up running into her…
-that's how it went.</t>
+          <t>Nono-chan was upstairs and Miru-chan, who was about
+to move from her hiding spot, ended up running into
+her… that's how it went.</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4175,8 +4177,8 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan decides the game's name and tells everyone in
-the chat.</t>
+          <t>Rin-chan decides the game's name and tells everyone
+in the chat.</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4589,8 +4591,8 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>However, when the hide-and-seek started up again, lies
-began flying everywhere.</t>
+          <t>However, when the hide-and-seek started up again,
+lies began flying everywhere.</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4957,8 +4959,8 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>Even as she thought that, she saw Miru-chan coming out
-the front door.</t>
+          <t>Even as she thought that, she saw Miru-chan coming
+out the front door.</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -5275,7 +5277,8 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>In the meantime, Rin-chan stays still between my legs.</t>
+          <t>In the meantime, Rin-chan stays still between my
+legs.</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5320,8 +5323,8 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, anxious that only Rin-chan is missing, says
-that and gets off the bus.</t>
+          <t>Miru-chan, anxious that only Rin-chan is missing,
+says that and gets off the bus.</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5460,8 +5463,8 @@
       <c r="B327" s="1" t="inlineStr">
         <is>
           <t>Her idea that increasing the places someone has to
-search will reduce the chance she'll come onto the bus
-is correct.</t>
+search will reduce the chance she'll come onto the
+bus is correct.</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5567,8 +5570,8 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>「That might be true... but, well, how should I put it,
-um... hmm...」</t>
+          <t>「That might be true... but, well, how should I put
+it, um... hmm...」</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5718,8 +5721,8 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t>「W-well, given our current position, of course it'd be
-bulging.」</t>
+          <t>「W-well, given our current position, of course it'd
+be bulging.」</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5855,8 +5858,8 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>I never imagined Rin-chan would actually say something
-like that.</t>
+          <t>I never imagined Rin-chan would actually say
+something like that.</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -6055,8 +6058,8 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>Being put on hold like that only makes my anticipation
-grow.</t>
+          <t>Being put on hold like that only makes my
+anticipation grow.</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -6147,8 +6150,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>Since she's about to do it for me, I selfishly think I
-can't risk spoiling Rin-chan's mood.</t>
+          <t>Since she's about to do it for me, I selfishly think
+I can't risk spoiling Rin-chan's mood.</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6514,8 +6517,8 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan turns her gaze to the game console resting on
-my stomach.</t>
+          <t>Rin-chan turns her gaze to the game console resting
+on my stomach.</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6545,8 +6548,8 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>Meanwhile, my penis, exposed to the air, is twitching,
-desperate to be sucked.</t>
+          <t>Meanwhile, my penis, exposed to the air, is
+twitching, desperate to be sucked.</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6914,7 +6917,8 @@
       </c>
       <c r="B422" s="1" t="inlineStr">
         <is>
-          <t>The contact between my penis and her mouth is amazing.</t>
+          <t>The contact between my penis and her mouth is
+amazing.</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -7159,8 +7163,8 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>「Ah, wait a sec… Nono-chan went to the bathroom… there
-we go」</t>
+          <t>「Ah, wait a sec… Nono-chan went to the bathroom…
+there we go」</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -7619,9 +7623,9 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>When that sensitive tip is sucked and then released...
-the sharpest stimulation hits, making me even more
-aroused.</t>
+          <t>When that sensitive tip is sucked and then
+released... the sharpest stimulation hits, making me
+even more aroused.</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7805,8 +7809,8 @@
       <c r="B480" s="1" t="inlineStr">
         <is>
           <t>The moment she looked at the screen, Rin-chan's
-expression changed and she hurriedly started typing in
-the chat.</t>
+expression changed and she hurriedly started typing
+in the chat.</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7896,8 +7900,8 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo started saying I might have been the one on
-the bus.」</t>
+          <t>「Rurichiyo started saying I might have been the one
+on the bus.」</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -8339,8 +8343,8 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>But this time she kept the tip in her mouth and licked
-the head with her tongue.</t>
+          <t>But this time she kept the tip in her mouth and
+licked the head with her tongue.</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -9196,7 +9200,8 @@
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... I can't take it anymore... I want to come...」</t>
+          <t>「Yeah... I can't take it anymore... I want to
+come...」</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -9887,8 +9892,8 @@
       <c r="B616" s="1" t="inlineStr">
         <is>
           <t>Rin-chan keeps it all in her mouth without letting a
-single drop escape, but taking all that cum looks like
-it’s really hard on her.</t>
+single drop escape, but taking all that cum looks
+like it’s really hard on her.</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -10344,9 +10349,9 @@
       </c>
       <c r="B646" s="1" t="inlineStr">
         <is>
-          <t>As expected, maybe it was too much to keep going while
-holding back my cum, so Rin-chan looked up and let go
-of the penis.</t>
+          <t>As expected, maybe it was too much to keep going
+while holding back my cum, so Rin-chan looked up and
+let go of the penis.</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -11076,7 +11081,8 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>「You really hid so well... I couldn't tell at all...！」</t>
+          <t>「You really hid so well... I couldn't tell at
+all...！」</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -11091,8 +11097,9 @@
       </c>
       <c r="B695" s="1" t="inlineStr">
         <is>
-          <t>But then it finally clicked. Rin-chan panicked because
-she’d seen that kind of exchange in the chat, right?</t>
+          <t>But then it finally clicked. Rin-chan panicked
+because she’d seen that kind of exchange in the chat,
+right?</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -11138,7 +11145,8 @@
       </c>
       <c r="B698" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan grumbles at Rin-chan hiding between my legs.</t>
+          <t>Miru-chan grumbles at Rin-chan hiding between my
+legs.</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -11200,8 +11208,8 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan finally climbed out of the driver's seat and,
-without the slightest remorse, said it flat out.</t>
+          <t>Rin-chan finally climbed out of the driver's seat
+and, without the slightest remorse, said it flat out.</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -11339,8 +11347,8 @@
       </c>
       <c r="B711" s="1" t="inlineStr">
         <is>
-          <t>「Haha, I'm tired too... I didn't expect it'd turn into
-such a brainy game.」</t>
+          <t>「Haha, I'm tired too... I didn't expect it'd turn
+into such a brainy game.」</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -11400,8 +11408,8 @@
       </c>
       <c r="B715" s="1" t="inlineStr">
         <is>
-          <t>「Yeah！ Pure Girl is about to start soon, so we have to
-hurry！」</t>
+          <t>「Yeah！ Pure Girl is about to start soon, so we have
+to hurry！」</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -11647,7 +11655,8 @@
       </c>
       <c r="B731" s="1" t="inlineStr">
         <is>
-          <t>Before I knew it I even had a cold sweat on my brow…….</t>
+          <t>Before I knew it I even had a cold sweat on my
+brow…….</t>
         </is>
       </c>
       <c r="C731" t="n">

--- a/processed_ruby_restored_xlsx/sc236_凛８：バスの中.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc236_凛８：バスの中.ss.xlsx
@@ -2075,8 +2075,8 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>I brought the game console from the room and set up a
-group chat with Miru-chan, Rin-chan, and four
+          <t>He brought the game console from the room and set up
+a group chat with Miru-chan, Rin-chan, and four
 consoles total.</t>
         </is>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="B132" s="1" t="inlineStr">
         <is>
           <t>If she went out of her way to volunteer, did she have
-a lot of confidence in hide-and-seek？</t>
+a lot of confidence in hide-and-seek？"</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>「Huh, how did you know？」</t>
+          <t>Huh, how did you know？</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3701,7 +3701,7 @@
         <is>
           <t>I get that she's being considerate of Nono-chan, who
 made herself the demon... but are they really going
-to sacrifice Miru-chan...?</t>
+to sacrifice Miru-chan...?"</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, you terrifying girl...！</t>
+          <t>Rin-chan, you terrifying girl...！"</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -6089,8 +6089,8 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>「Geez, Niini, you're so naughty that you won't settle
-down unless I give you kisses, right？」</t>
+          <t>Geez, Niini, you're so naughty that you won't settle
+down unless I give you kisses, right？</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>The penis pulled out from my trousers snaps up,
+          <t>The penis pulled out from his trousers snaps up,
 pointing straight up.</t>
         </is>
       </c>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>With my attention drifting here and there,
+          <t>With his attention drifting here and there,
 Rin-chan—who saw that sight right in front of
 her—suddenly panicked and hesitated a little.</t>
         </is>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh！ Nn, chuu！ Chup！ Chuch！」</t>
+          <t>Nnnh！ Nn, chuu！ Chup！ Chuch！</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>「Ah... that's good...」</t>
+          <t>Ah... that's good...</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -7624,7 +7624,7 @@
       <c r="B468" s="1" t="inlineStr">
         <is>
           <t>When that sensitive tip is sucked and then
-released... the sharpest stimulation hits, making me
+released... the sharpest stimulation hits, making him
 even more aroused.</t>
         </is>
       </c>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>「Nn...！　Nfufuu~！　Pua！」</t>
+          <t>Nn...！　Nfufuu~！　Pua！</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>「Nnna...！」</t>
+          <t>Nnna...！</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>「Kufu, Nono-chan's kinda easy...」</t>
+          <t>Kufu, Nono-chan's kinda easy...</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="B567" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Rin-chan, geez...」</t>
+          <t>Ah... Rin-chan, geez...</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>「What is it, Niini... can't hold it anymore？」</t>
+          <t>What is it, Niini... can't hold it anymore？</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="B589" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh…！」</t>
+          <t>Nnngh…！</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>「Nnffah！？ Ah... ah, ahfu, fuh... nn...」</t>
+          <t>Nnffah！？ Ah... ah, ahfu, fuh... nn...</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="B612" s="1" t="inlineStr">
         <is>
-          <t>「Whoa...！」</t>
+          <t>Whoa...！</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, mmm—... Ahf！ Fuu...！」</t>
+          <t>Mmm, mmm—... Ahf！ Fuu...！</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="B634" s="1" t="inlineStr">
         <is>
-          <t>The way her tongue moves like it's cleaning feels
+          <t>The way their tongue moves like it's cleaning feels
 really nice, a mellow kind of stimulation.</t>
         </is>
       </c>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="B639" s="1" t="inlineStr">
         <is>
-          <t>「Mmmfuu？ Sqqch！ Glurgh！ Squ, squ！」</t>
+          <t>Mmmfuu？ Sqqch！ Glurgh！ Squ, squ！</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="B645" s="1" t="inlineStr">
         <is>
-          <t>「Nngh...ppa！　Nfu...nfufu...」</t>
+          <t>Nngh...ppa！　Nfu...nfufu...</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -10350,7 +10350,7 @@
       <c r="B646" s="1" t="inlineStr">
         <is>
           <t>As expected, maybe it was too much to keep going
-while holding back my cum, so Rin-chan looked up and
+while holding back his cum, so Rin-chan looked up and
 let go of the penis.</t>
         </is>
       </c>
@@ -10457,7 +10457,7 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>「Nng…？」</t>
+          <t>Nng…？</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="B655" s="1" t="inlineStr">
         <is>
-          <t>「nngh... nngh‑fu... nngh‑fuh, nngh‑uu, fuu, fuu...」</t>
+          <t>nngh... nngh‑fu... nngh‑fuh, nngh‑uu, fuu, fuu...</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
-          <t>「Well, I wonder what happened to everyone…」</t>
+          <t>Well, I wonder what happened to everyone…</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="B706" s="1" t="inlineStr">
         <is>
-          <t>「Ah... now that you mention it, that's right.」</t>
+          <t>Ah... now that you mention it, that's right.</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="B721" s="1" t="inlineStr">
         <is>
-          <t>「Well then, I'll be leaving before you.」</t>
+          <t>Well then, I'll be leaving before you.</t>
         </is>
       </c>
       <c r="C721" t="n">
